--- a/files/pokemon.xlsx
+++ b/files/pokemon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/70db758b79a2d8f8/Documents/Dan/test_scripts/project/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="125" documentId="14_{3214C9CA-E3F8-4F01-9D63-E4C439A0136D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCA24D15-AE2A-419A-B809-1A6647D341DF}"/>
+  <xr:revisionPtr revIDLastSave="133" documentId="14_{3214C9CA-E3F8-4F01-9D63-E4C439A0136D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C64CA66F-9311-4452-8119-0C5846C8F5A1}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{686FD583-654D-4DE9-AC6B-9DF537E0A97A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{686FD583-654D-4DE9-AC6B-9DF537E0A97A}"/>
   </bookViews>
   <sheets>
     <sheet name="Pokemon Cards" sheetId="1" r:id="rId1"/>
@@ -422,6 +422,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/files/pokemon.xlsx
+++ b/files/pokemon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/70db758b79a2d8f8/Documents/Dan/test_scripts/project/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E886035E-F80C-4B92-B8A9-2D1EE1C9277D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="8_{E886035E-F80C-4B92-B8A9-2D1EE1C9277D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A427283-E0DD-40F0-AD90-796D55970CCA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{686FD583-654D-4DE9-AC6B-9DF537E0A97A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="97">
   <si>
     <t>Card</t>
   </si>
@@ -323,6 +323,12 @@
   <si>
     <t>4th Print</t>
   </si>
+  <si>
+    <t>Golem</t>
+  </si>
+  <si>
+    <t>Uncommon</t>
+  </si>
 </sst>
 </file>
 
@@ -440,10 +446,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -983,11 +985,15 @@
       <c r="J2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="1"/>
+      <c r="K2" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="L2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>90</v>
+      </c>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
@@ -2687,29 +2693,65 @@
       <c r="AR22" s="1"/>
     </row>
     <row r="23" spans="1:44" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
+      <c r="A23" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" s="1">
+        <v>1999</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="1">
+        <v>8</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
+      <c r="I23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>96</v>
+      </c>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
-      <c r="Q23" s="1"/>
-      <c r="R23" s="1"/>
-      <c r="S23" s="1"/>
-      <c r="T23" s="1"/>
-      <c r="U23" s="1"/>
-      <c r="V23" s="1"/>
-      <c r="W23" s="1"/>
+      <c r="Q23" s="1">
+        <v>18</v>
+      </c>
+      <c r="R23" s="1">
+        <v>0</v>
+      </c>
+      <c r="S23" s="1">
+        <v>18</v>
+      </c>
+      <c r="T23" s="3">
+        <v>45950</v>
+      </c>
+      <c r="U23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="V23" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="W23" s="4" t="s">
+        <v>70</v>
+      </c>
       <c r="X23" s="1"/>
       <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
@@ -47730,9 +47772,10 @@
     <hyperlink ref="W20" r:id="rId6" xr:uid="{193394C9-071F-4510-B788-47592010CC50}"/>
     <hyperlink ref="W21" r:id="rId7" xr:uid="{5DE3BF49-67F2-4D39-BA84-888EE9DA0B02}"/>
     <hyperlink ref="W22" r:id="rId8" xr:uid="{51D31016-EF93-40CA-A53A-7A1DB2AF88BF}"/>
+    <hyperlink ref="W23" r:id="rId9" xr:uid="{B14AFC6E-B7B9-4FFF-8AA9-A9E268A7B575}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId10"/>
 </worksheet>
 </file>
 
@@ -47753,7 +47796,7 @@
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2">
         <f>SUM('Pokemon Cards'!S:S)</f>
-        <v>672.80000000000007</v>
+        <v>690.80000000000007</v>
       </c>
     </row>
   </sheetData>
